--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sem5\datathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA08D646-2625-4FBE-A86D-AE897058EA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8DF223-6DE7-49BA-87A7-8DFBE0B0885D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{500EC2CD-AC47-458C-A7EC-B7D16D7FB4B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{500EC2CD-AC47-458C-A7EC-B7D16D7FB4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,26 +35,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
   <si>
     <t>Smote</t>
   </si>
   <si>
-    <t xml:space="preserve">RUS </t>
-  </si>
-  <si>
-    <t>Smote+RUS</t>
-  </si>
-  <si>
     <t>LightGBM</t>
   </si>
   <si>
     <t>No Sampling</t>
   </si>
   <si>
-    <t>5-fold cross validation(AUROC)</t>
-  </si>
-  <si>
     <t>5-fold cross validation (Accuracy)</t>
   </si>
   <si>
@@ -70,16 +61,25 @@
     <t>SVM (Rbf)</t>
   </si>
   <si>
-    <t>REMOVING 4 Redundant features using correlation analysus</t>
-  </si>
-  <si>
     <t>Random Forest</t>
   </si>
   <si>
     <t>XGBoost</t>
   </si>
   <si>
-    <t>REMOVING 4 Redundant features using RFE</t>
+    <t>Removing 4 Redundant features using correlation analysis</t>
+  </si>
+  <si>
+    <t>Removing 4 Redundant features using RFE</t>
+  </si>
+  <si>
+    <t>5-fold cross validation(AUC- ROC)</t>
+  </si>
+  <si>
+    <t>Tomek</t>
+  </si>
+  <si>
+    <t>Smote+Tomek</t>
   </si>
 </sst>
 </file>
@@ -95,12 +95,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -135,13 +141,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,6 +470,8 @@
     <col min="2" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" customWidth="1"/>
     <col min="14" max="14" width="13.5546875" customWidth="1"/>
     <col min="15" max="15" width="13.44140625" customWidth="1"/>
   </cols>
@@ -470,14 +479,14 @@
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -489,46 +498,46 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
         <v>0.83489999999999998</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>0.84819999999999995</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>0.83599999999999997</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>0.84870000000000001</v>
       </c>
       <c r="K3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0.86080000000000001</v>
@@ -545,7 +554,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>0.8226</v>
@@ -560,7 +569,7 @@
         <v>0.82850000000000001</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>0.74370000000000003</v>
@@ -577,7 +586,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>0.81720000000000004</v>
@@ -591,8 +600,11 @@
       <c r="E5">
         <v>0.82299999999999995</v>
       </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>0.73799999999999999</v>
@@ -607,12 +619,12 @@
         <v>0.86870000000000003</v>
       </c>
       <c r="P5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>0.83109999999999995</v>
@@ -627,7 +639,7 @@
         <v>0.83220000000000005</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>0.83399999999999996</v>
@@ -644,7 +656,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0.82389999999999997</v>
@@ -658,8 +670,11 @@
       <c r="E7">
         <v>0.83120000000000005</v>
       </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>0.82720000000000005</v>
@@ -674,12 +689,12 @@
         <v>0.86809999999999998</v>
       </c>
       <c r="P7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>0.81069999999999998</v>
@@ -693,8 +708,11 @@
       <c r="E8">
         <v>0.81440000000000001</v>
       </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>0.80789999999999995</v>
@@ -709,12 +727,12 @@
         <v>0.86760000000000004</v>
       </c>
       <c r="P8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>0.8206</v>
@@ -722,14 +740,14 @@
       <c r="C9">
         <v>0.81269999999999998</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>0.83189999999999997</v>
       </c>
       <c r="E9">
         <v>0.82289999999999996</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>0.85509999999999997</v>
@@ -746,7 +764,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>0.81410000000000005</v>
@@ -760,8 +778,11 @@
       <c r="E10">
         <v>0.81740000000000002</v>
       </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>0.83360000000000001</v>
@@ -776,7 +797,7 @@
         <v>0.86480000000000001</v>
       </c>
       <c r="P10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
